--- a/Docs/Comparació Simulacio Vendes.xlsx
+++ b/Docs/Comparació Simulacio Vendes.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Temp\____\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Temp\____\InversionsV2.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B067B2-5807-4A84-8085-EC5AC1B5F8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48F8A44-BE72-42B5-BE68-519180BE659B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="0" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{CFE75038-AD5F-4A09-ACF9-52DE856301C2}"/>
+    <workbookView xWindow="22932" yWindow="0" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{CFE75038-AD5F-4A09-ACF9-52DE856301C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="24">
   <si>
     <t>Fons Orig</t>
   </si>
@@ -81,14 +82,31 @@
   <si>
     <t>Trea Renta Fija Ahorro S FI</t>
   </si>
+  <si>
+    <t>PiG Prod</t>
+  </si>
+  <si>
+    <t>PiG Orig</t>
+  </si>
+  <si>
+    <t>ntbPigSimulacio</t>
+  </si>
+  <si>
+    <t>ntbPigOrigSimulacio</t>
+  </si>
+  <si>
+    <t>_PigDeLaCompraOrigen</t>
+  </si>
+  <si>
+    <t>&lt;--PiG de la compra parts disponibles per 4,2296 parts</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ _€"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -138,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -159,10 +177,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1983,10 +2010,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C329D19-2A9A-43FE-BA45-56EBB9C868C1}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.90625" customWidth="1"/>
+    <col min="1" max="1" width="23.90625" style="14" customWidth="1"/>
     <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.1796875" customWidth="1"/>
     <col min="4" max="4" width="6.81640625" bestFit="1" customWidth="1"/>
@@ -1999,13 +2026,13 @@
     <col min="11" max="11" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="2" customWidth="1"/>
     <col min="13" max="13" width="6.26953125" customWidth="1"/>
-    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="2" customWidth="1"/>
-    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
@@ -2049,7 +2076,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B2">
@@ -2090,7 +2117,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B3">
@@ -2131,7 +2158,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B4">
@@ -2172,7 +2199,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B5">
@@ -2213,7 +2240,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B6">
@@ -2254,7 +2281,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B7">
@@ -2295,7 +2322,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B8">
@@ -2336,7 +2363,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" s="14" t="s">
         <v>14</v>
       </c>
       <c r="B9">
@@ -2377,7 +2404,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B10">
@@ -2418,7 +2445,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" s="14" t="s">
         <v>16</v>
       </c>
       <c r="B11">
@@ -2459,7 +2486,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B12">
@@ -2499,17 +2526,1015 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10">
+        <v>217</v>
+      </c>
+      <c r="C14" s="11">
+        <v>44725</v>
+      </c>
+      <c r="D14" s="10">
+        <v>23.23</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12">
+        <v>958.5</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10">
+        <v>16</v>
+      </c>
+      <c r="I14" s="11">
+        <v>41166</v>
+      </c>
+      <c r="J14" s="12">
+        <v>8238.17</v>
+      </c>
+      <c r="K14" s="12">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10">
+        <v>4.2295999999999996</v>
+      </c>
+      <c r="N14" s="12">
+        <v>1499.96</v>
+      </c>
+      <c r="O14" s="10"/>
+      <c r="P14" s="12">
+        <v>2007.13</v>
+      </c>
+    </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C15" s="11"/>
-      <c r="K15" s="2"/>
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10">
+        <v>1235</v>
+      </c>
+      <c r="C15" s="11">
+        <v>44893</v>
+      </c>
+      <c r="D15" s="10">
+        <v>21.81</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1.5729500000000001</v>
+      </c>
+      <c r="F15" s="12">
+        <v>894.74</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10">
+        <v>16</v>
+      </c>
+      <c r="I15" s="11">
+        <v>41166</v>
+      </c>
+      <c r="J15" s="12">
+        <v>7452.45</v>
+      </c>
+      <c r="K15" s="12">
+        <v>537.47</v>
+      </c>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10">
+        <v>20.23705</v>
+      </c>
+      <c r="N15" s="12">
+        <v>6914.98</v>
+      </c>
+      <c r="O15" s="10"/>
+      <c r="P15" s="12">
+        <v>9603.3799999999992</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="K16" s="2"/>
-    </row>
-    <row r="20" spans="11:11" x14ac:dyDescent="0.35">
-      <c r="K20" s="2">
-        <f>C15-SUM(K15:K19)</f>
-        <v>0</v>
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="10">
+        <v>1239</v>
+      </c>
+      <c r="C16" s="11">
+        <v>44893</v>
+      </c>
+      <c r="D16" s="10">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="E16" s="10">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F16" s="12">
+        <v>0.02</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10">
+        <v>16</v>
+      </c>
+      <c r="I16" s="11">
+        <v>41166</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10">
+        <v>0</v>
+      </c>
+      <c r="N16" s="12">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10"/>
+      <c r="P16" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="10">
+        <v>1241</v>
+      </c>
+      <c r="C17" s="11">
+        <v>44939</v>
+      </c>
+      <c r="D17" s="10">
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="E17" s="10">
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="F17" s="12">
+        <v>80.64</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10">
+        <v>16</v>
+      </c>
+      <c r="I17" s="11">
+        <v>41166</v>
+      </c>
+      <c r="J17" s="12">
+        <v>681.34</v>
+      </c>
+      <c r="K17" s="12">
+        <v>681.34</v>
+      </c>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10">
+        <v>0</v>
+      </c>
+      <c r="N17" s="12">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10"/>
+      <c r="P17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10">
+        <v>197</v>
+      </c>
+      <c r="C18" s="11">
+        <v>44473</v>
+      </c>
+      <c r="D18" s="10">
+        <v>24.54</v>
+      </c>
+      <c r="E18" s="10">
+        <v>24.54</v>
+      </c>
+      <c r="F18" s="12">
+        <v>967.91</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10">
+        <v>17</v>
+      </c>
+      <c r="I18" s="11">
+        <v>41377</v>
+      </c>
+      <c r="J18" s="12">
+        <v>7163.17</v>
+      </c>
+      <c r="K18" s="12">
+        <v>7163.17</v>
+      </c>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10">
+        <v>0</v>
+      </c>
+      <c r="N18" s="12">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10"/>
+      <c r="P18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="10">
+        <v>205</v>
+      </c>
+      <c r="C19" s="11">
+        <v>44524</v>
+      </c>
+      <c r="D19" s="10">
+        <v>46.265999999999998</v>
+      </c>
+      <c r="E19" s="10">
+        <v>46.265999999999998</v>
+      </c>
+      <c r="F19" s="12">
+        <v>1840.76</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10">
+        <v>17</v>
+      </c>
+      <c r="I19" s="11">
+        <v>41377</v>
+      </c>
+      <c r="J19" s="12">
+        <v>14111.52</v>
+      </c>
+      <c r="K19" s="12">
+        <v>14111.52</v>
+      </c>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10">
+        <v>0</v>
+      </c>
+      <c r="N19" s="12">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10"/>
+      <c r="P19" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="10">
+        <v>1241</v>
+      </c>
+      <c r="C20" s="11">
+        <v>44939</v>
+      </c>
+      <c r="D20" s="10">
+        <v>1.1525000000000001</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1.1525000000000001</v>
+      </c>
+      <c r="F20" s="12">
+        <v>46.21</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10">
+        <v>17</v>
+      </c>
+      <c r="I20" s="11">
+        <v>41377</v>
+      </c>
+      <c r="J20" s="12">
+        <v>186.29</v>
+      </c>
+      <c r="K20" s="12">
+        <v>186.29</v>
+      </c>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10">
+        <v>0</v>
+      </c>
+      <c r="N20" s="12">
+        <v>0</v>
+      </c>
+      <c r="O20" s="10"/>
+      <c r="P20" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="10">
+        <v>203</v>
+      </c>
+      <c r="C21" s="11">
+        <v>44496</v>
+      </c>
+      <c r="D21" s="10">
+        <v>29.760999999999999</v>
+      </c>
+      <c r="E21" s="10">
+        <v>29.760999999999999</v>
+      </c>
+      <c r="F21" s="12">
+        <v>1178.46</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10">
+        <v>7</v>
+      </c>
+      <c r="I21" s="11">
+        <v>41492</v>
+      </c>
+      <c r="J21" s="12">
+        <v>8611.7000000000007</v>
+      </c>
+      <c r="K21" s="12">
+        <v>8611.7000000000007</v>
+      </c>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10">
+        <v>0</v>
+      </c>
+      <c r="N21" s="12">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10"/>
+      <c r="P21" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="10">
+        <v>1241</v>
+      </c>
+      <c r="C22" s="11">
+        <v>44939</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0.64380000000000004</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0.64380000000000004</v>
+      </c>
+      <c r="F22" s="12">
+        <v>25.81</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10">
+        <v>27</v>
+      </c>
+      <c r="I22" s="11">
+        <v>41521</v>
+      </c>
+      <c r="J22" s="12">
+        <v>82.89</v>
+      </c>
+      <c r="K22" s="12">
+        <v>82.89</v>
+      </c>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10">
+        <v>0</v>
+      </c>
+      <c r="N22" s="12">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10"/>
+      <c r="P22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="10">
+        <v>203</v>
+      </c>
+      <c r="C23" s="11">
+        <v>44496</v>
+      </c>
+      <c r="D23" s="10">
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="E23" s="10">
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="F23" s="12">
+        <v>196.52</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10">
+        <v>37</v>
+      </c>
+      <c r="I23" s="11">
+        <v>41534</v>
+      </c>
+      <c r="J23" s="12">
+        <v>1355.16</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1355.16</v>
+      </c>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10">
+        <v>0</v>
+      </c>
+      <c r="N23" s="12">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10"/>
+      <c r="P23" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="10">
+        <v>1241</v>
+      </c>
+      <c r="C24" s="11">
+        <v>44939</v>
+      </c>
+      <c r="D24" s="10">
+        <v>2.0644</v>
+      </c>
+      <c r="E24" s="10">
+        <v>2.0644</v>
+      </c>
+      <c r="F24" s="12">
+        <v>82.77</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10">
+        <v>108</v>
+      </c>
+      <c r="I24" s="11">
+        <v>42387</v>
+      </c>
+      <c r="J24" s="12">
+        <v>-20.350000000000001</v>
+      </c>
+      <c r="K24" s="12">
+        <v>-20.350000000000001</v>
+      </c>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10">
+        <v>0</v>
+      </c>
+      <c r="N24" s="12">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10"/>
+      <c r="P24" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="N25" s="2">
+        <f>SUM(N14:N24)</f>
+        <v>8414.9399999999987</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="N26" s="12">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D525199C-3D0C-43C0-9DE5-99B4BC498312}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="17.6328125" customWidth="1"/>
+    <col min="11" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4">
+        <v>217</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5">
+        <v>41166</v>
+      </c>
+      <c r="E2" s="5">
+        <v>44725</v>
+      </c>
+      <c r="F2" s="4">
+        <v>23.23</v>
+      </c>
+      <c r="G2" s="4">
+        <v>4.2295999999999996</v>
+      </c>
+      <c r="H2" s="6">
+        <v>8240.17</v>
+      </c>
+      <c r="I2" s="6">
+        <v>1500.33</v>
+      </c>
+      <c r="J2" s="6">
+        <v>174.88</v>
+      </c>
+      <c r="K2" s="6">
+        <v>2007.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1235</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5">
+        <v>41166</v>
+      </c>
+      <c r="E3" s="5">
+        <v>44893</v>
+      </c>
+      <c r="F3" s="4">
+        <v>21.81</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.77039999999999997</v>
+      </c>
+      <c r="H3" s="6">
+        <v>7454.33</v>
+      </c>
+      <c r="I3" s="6">
+        <v>263.31</v>
+      </c>
+      <c r="J3" s="6">
+        <v>31.67</v>
+      </c>
+      <c r="K3" s="6">
+        <v>365.66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1239</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5">
+        <v>41166</v>
+      </c>
+      <c r="E4" s="5">
+        <v>44893</v>
+      </c>
+      <c r="F4" s="4">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1241</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5">
+        <v>41166</v>
+      </c>
+      <c r="E5" s="5">
+        <v>44939</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>681.51</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4">
+        <v>197</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="5">
+        <v>41377</v>
+      </c>
+      <c r="E6" s="5">
+        <v>44473</v>
+      </c>
+      <c r="F6" s="4">
+        <v>24.54</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>7165.29</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>17</v>
+      </c>
+      <c r="B7" s="4">
+        <v>205</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="5">
+        <v>41377</v>
+      </c>
+      <c r="E7" s="5">
+        <v>44524</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46.265999999999998</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>14115.51</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>17</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1241</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5">
+        <v>41377</v>
+      </c>
+      <c r="E8" s="5">
+        <v>44939</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1.1525000000000001</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>186.39</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4">
+        <v>203</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="5">
+        <v>41492</v>
+      </c>
+      <c r="E9" s="5">
+        <v>44496</v>
+      </c>
+      <c r="F9" s="4">
+        <v>29.760999999999999</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>8614.27</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>27</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1241</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="5">
+        <v>41521</v>
+      </c>
+      <c r="E10" s="5">
+        <v>44939</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.64380000000000004</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>82.95</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4">
+        <v>203</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5">
+        <v>41534</v>
+      </c>
+      <c r="E11" s="5">
+        <v>44496</v>
+      </c>
+      <c r="F11" s="4">
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1355.59</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>108</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1241</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5">
+        <v>42387</v>
+      </c>
+      <c r="E12" s="5">
+        <v>44939</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2.0644</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>-20.170000000000002</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I13" s="2">
+        <f>SUM(I2:I12)</f>
+        <v>1763.6399999999999</v>
+      </c>
+      <c r="J13" s="2">
+        <f>SUM(J2:J12)</f>
+        <v>206.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I18">
+        <v>24.466652410874399</v>
+      </c>
+      <c r="J18" s="12">
+        <v>433.28309999999999</v>
+      </c>
+      <c r="K18">
+        <v>23.23</v>
+      </c>
+    </row>
+    <row r="19" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I19">
+        <v>474.54419999999999</v>
+      </c>
+      <c r="J19">
+        <v>474.54419999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I20">
+        <f>+I18*I19</f>
+        <v>11610.507994996462</v>
+      </c>
+      <c r="J20" s="2">
+        <f>(J19-J18)*K18</f>
+        <v>958.49535300000002</v>
+      </c>
+      <c r="K20">
+        <v>4.2295999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="2">
+        <f>J20/K18*K20</f>
+        <v>174.51794855999998</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
